--- a/design_issues/sonarqube/P6_FormPlugin.xlsx
+++ b/design_issues/sonarqube/P6_FormPlugin.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Issues" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="121">
   <si>
     <t>severity</t>
   </si>
@@ -88,48 +88,39 @@
     <t>Unexpected duplicate selector ".field-config-section h4", first used at line 1075</t>
   </si>
   <si>
+    <t>admin/views/forms-list.php</t>
+  </si>
+  <si>
+    <t>A form label must be associated with a control.</t>
+  </si>
+  <si>
+    <t>5min</t>
+  </si>
+  <si>
+    <t>admin/views/submissions.php</t>
+  </si>
+  <si>
+    <t>Use &lt;address&gt; or &lt;details&gt; or &lt;fieldset&gt; or &lt;optgroup&gt; instead of the group role to ensure accessibility across all devices.</t>
+  </si>
+  <si>
+    <t>form-plugin.php</t>
+  </si>
+  <si>
+    <t>Replace "require_once" with namespace import mechanism through the "use" keyword.</t>
+  </si>
+  <si>
+    <t>includes/class-admin.php</t>
+  </si>
+  <si>
+    <t>Class "Form_Plugin_Admin" has 32 methods, which is greater than 20 authorized. Split it into smaller classes.</t>
+  </si>
+  <si>
+    <t>1h</t>
+  </si>
+  <si>
     <t>MINOR</t>
   </si>
   <si>
-    <t>admin/views/form-builder.php</t>
-  </si>
-  <si>
-    <t>Remove the useless trailing whitespaces at the end of this line.</t>
-  </si>
-  <si>
-    <t>admin/views/forms-list.php</t>
-  </si>
-  <si>
-    <t>A form label must be associated with a control.</t>
-  </si>
-  <si>
-    <t>5min</t>
-  </si>
-  <si>
-    <t>admin/views/submissions.php</t>
-  </si>
-  <si>
-    <t>Add a new line at the end of this file.</t>
-  </si>
-  <si>
-    <t>Use &lt;address&gt; or &lt;details&gt; or &lt;fieldset&gt; or &lt;optgroup&gt; instead of the group role to ensure accessibility across all devices.</t>
-  </si>
-  <si>
-    <t>form-plugin.php</t>
-  </si>
-  <si>
-    <t>Replace "require_once" with namespace import mechanism through the "use" keyword.</t>
-  </si>
-  <si>
-    <t>includes/class-admin.php</t>
-  </si>
-  <si>
-    <t>Class "Form_Plugin_Admin" has 32 methods, which is greater than 20 authorized. Split it into smaller classes.</t>
-  </si>
-  <si>
-    <t>1h</t>
-  </si>
-  <si>
     <t>Remove this unused "$forms" local variable.</t>
   </si>
   <si>
@@ -292,9 +283,6 @@
     <t>Define a constant instead of duplicating this literal "1.4.0" 3 times.</t>
   </si>
   <si>
-    <t>Either remove this useless object instantiation of class "Form_Plugin_Form_Renderer" or use it</t>
-  </si>
-  <si>
     <t>includes/class-form-renderer.php</t>
   </si>
   <si>
@@ -373,12 +361,21 @@
     <t>Refactor this function to reduce its Cognitive Complexity from ... to the 15 allowed.</t>
   </si>
   <si>
+    <t>Remove this unused "..." local variable.</t>
+  </si>
+  <si>
     <t>Unexpected duplicate selector "...", first used at line ...</t>
   </si>
   <si>
+    <t>Immediately return this expression instead of assigning it to the temporary variable "...".</t>
+  </si>
+  <si>
     <t>Class "..." has ... methods, which is greater than 20 authorized. Split it into smaller classes.</t>
   </si>
   <si>
+    <t>Remove the unused function parameter "...".</t>
+  </si>
+  <si>
     <t>Use &lt;address&gt; or &lt;details&gt; or &lt;fieldset&gt; or &lt;optgroup&gt; instead of the group role to ensure accessibility across all devices.</t>
   </si>
   <si>
@@ -386,33 +383,19 @@
   </si>
   <si>
     <t>Remove this unused private "..." method.</t>
-  </si>
-  <si>
-    <t>Remove the unused function parameter "...".</t>
-  </si>
-  <si>
-    <t>Immediately return this expression instead of assigning it to the temporary variable "...".</t>
-  </si>
-  <si>
-    <t>Remove this unused "..." local variable.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -441,16 +424,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -458,18 +441,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -772,13 +746,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="28.54296875" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" customWidth="1"/>
-    <col min="5" max="5" width="72.90625" customWidth="1"/>
-    <col min="6" max="6" width="16.90625" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="20.453125" customWidth="1"/>
+    <col min="5" max="5" width="103.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -1013,436 +987,439 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
         <v>22</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>108</v>
+      </c>
+      <c r="E11" t="s">
         <v>23</v>
       </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
       <c r="F11" t="s">
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
       </c>
       <c r="D12">
-        <v>48</v>
+        <v>212</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
       </c>
       <c r="D13">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
         <v>9</v>
       </c>
       <c r="D14">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>
       </c>
       <c r="D15">
-        <v>124</v>
+        <v>204</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
         <v>9</v>
       </c>
       <c r="D16">
-        <v>108</v>
+        <v>205</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s">
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
       </c>
+      <c r="D17">
+        <v>207</v>
+      </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
         <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
       </c>
       <c r="D18">
-        <v>74</v>
+        <v>207</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
         <v>9</v>
       </c>
       <c r="D19">
-        <v>75</v>
+        <v>215</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
         <v>9</v>
       </c>
       <c r="D20">
-        <v>81</v>
+        <v>221</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
         <v>9</v>
       </c>
       <c r="D21">
-        <v>87</v>
+        <v>221</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
       </c>
       <c r="D22">
-        <v>129</v>
+        <v>231</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s">
         <v>11</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
       </c>
       <c r="D23">
-        <v>173</v>
+        <v>234</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F23" t="s">
         <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
       </c>
       <c r="D24">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G24" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
       </c>
       <c r="D25">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F25" t="s">
         <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
       </c>
       <c r="D26">
-        <v>218</v>
+        <v>251</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F26" t="s">
         <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
       </c>
       <c r="D27">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s">
         <v>11</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
       </c>
       <c r="D28">
-        <v>298</v>
+        <v>254</v>
       </c>
       <c r="E28" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
       </c>
       <c r="D29">
-        <v>32</v>
+        <v>330</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -1450,137 +1427,137 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
       </c>
       <c r="D30">
-        <v>17</v>
+        <v>483</v>
       </c>
       <c r="E30" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F30" t="s">
         <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
       </c>
       <c r="D31">
-        <v>204</v>
+        <v>483</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F31" t="s">
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
         <v>9</v>
       </c>
       <c r="D32">
-        <v>205</v>
+        <v>498</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F32" t="s">
         <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
       </c>
       <c r="D33">
-        <v>207</v>
+        <v>503</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
       </c>
       <c r="G33" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
         <v>9</v>
       </c>
       <c r="D34">
-        <v>207</v>
+        <v>688</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F34" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
       </c>
       <c r="D35">
-        <v>215</v>
+        <v>792</v>
       </c>
       <c r="E35" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F35" t="s">
         <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -1588,344 +1565,344 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
         <v>9</v>
       </c>
       <c r="D36">
-        <v>221</v>
+        <v>792</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
       </c>
       <c r="D37">
-        <v>221</v>
+        <v>800</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F37" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
       </c>
       <c r="D38">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="E38" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F38" t="s">
         <v>11</v>
       </c>
       <c r="G38" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
       </c>
       <c r="D39">
-        <v>234</v>
+        <v>419</v>
       </c>
       <c r="E39" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F39" t="s">
         <v>11</v>
       </c>
       <c r="G39" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
         <v>9</v>
       </c>
       <c r="D40">
-        <v>236</v>
+        <v>454</v>
       </c>
       <c r="E40" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="F40" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
       </c>
       <c r="D41">
-        <v>236</v>
+        <v>459</v>
       </c>
       <c r="E41" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F41" t="s">
         <v>11</v>
       </c>
       <c r="G41" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
       </c>
       <c r="D42">
-        <v>251</v>
+        <v>465</v>
       </c>
       <c r="E42" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="F42" t="s">
         <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
       </c>
       <c r="D43">
-        <v>254</v>
+        <v>465</v>
       </c>
       <c r="E43" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="F43" t="s">
         <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
       </c>
       <c r="D44">
-        <v>254</v>
+        <v>474</v>
       </c>
       <c r="E44" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F44" t="s">
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
       </c>
       <c r="D45">
-        <v>309</v>
+        <v>597</v>
       </c>
       <c r="E45" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
       </c>
       <c r="D46">
-        <v>310</v>
+        <v>706</v>
       </c>
       <c r="E46" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="F46" t="s">
         <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
       </c>
       <c r="D47">
-        <v>311</v>
+        <v>817</v>
       </c>
       <c r="E47" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
         <v>9</v>
       </c>
       <c r="D48">
-        <v>312</v>
+        <v>834</v>
       </c>
       <c r="E48" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="F48" t="s">
         <v>11</v>
       </c>
       <c r="G48" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
       </c>
       <c r="D49">
-        <v>313</v>
+        <v>847</v>
       </c>
       <c r="E49" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="F49" t="s">
         <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C50" t="s">
         <v>9</v>
       </c>
       <c r="D50">
-        <v>330</v>
+        <v>926</v>
       </c>
       <c r="E50" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="F50" t="s">
         <v>11</v>
       </c>
       <c r="G50" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -1933,22 +1910,22 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="C51" t="s">
         <v>9</v>
       </c>
       <c r="D51">
-        <v>483</v>
+        <v>40</v>
       </c>
       <c r="E51" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F51" t="s">
         <v>11</v>
       </c>
       <c r="G51" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -1956,160 +1933,160 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="C52" t="s">
         <v>9</v>
       </c>
       <c r="D52">
-        <v>483</v>
+        <v>46</v>
       </c>
       <c r="E52" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="F52" t="s">
         <v>11</v>
       </c>
       <c r="G52" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="C53" t="s">
         <v>9</v>
       </c>
       <c r="D53">
-        <v>498</v>
+        <v>181</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="F53" t="s">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="C54" t="s">
         <v>9</v>
       </c>
       <c r="D54">
-        <v>503</v>
+        <v>200</v>
       </c>
       <c r="E54" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F54" t="s">
         <v>11</v>
       </c>
       <c r="G54" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="C55" t="s">
         <v>9</v>
       </c>
       <c r="D55">
-        <v>688</v>
+        <v>74</v>
       </c>
       <c r="E55" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="F55" t="s">
         <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="C56" t="s">
         <v>9</v>
       </c>
       <c r="D56">
-        <v>792</v>
+        <v>86</v>
       </c>
       <c r="E56" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F56" t="s">
         <v>11</v>
       </c>
       <c r="G56" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
         <v>9</v>
       </c>
       <c r="D57">
-        <v>792</v>
+        <v>92</v>
       </c>
       <c r="E57" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F57" t="s">
         <v>11</v>
       </c>
       <c r="G57" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="C58" t="s">
         <v>9</v>
       </c>
       <c r="D58">
-        <v>800</v>
+        <v>93</v>
       </c>
       <c r="E58" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="F58" t="s">
         <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -2117,344 +2094,344 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
         <v>9</v>
       </c>
       <c r="D59">
-        <v>17</v>
+        <v>440</v>
       </c>
       <c r="E59" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F59" t="s">
         <v>11</v>
       </c>
       <c r="G59" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C60" t="s">
         <v>9</v>
       </c>
       <c r="D60">
-        <v>419</v>
+        <v>503</v>
       </c>
       <c r="E60" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="F60" t="s">
         <v>11</v>
       </c>
       <c r="G60" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C61" t="s">
         <v>9</v>
       </c>
       <c r="D61">
-        <v>421</v>
+        <v>575</v>
       </c>
       <c r="E61" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F61" t="s">
         <v>11</v>
       </c>
       <c r="G61" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C62" t="s">
         <v>9</v>
       </c>
       <c r="D62">
-        <v>422</v>
+        <v>66</v>
       </c>
       <c r="E62" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F62" t="s">
         <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C63" t="s">
         <v>9</v>
       </c>
       <c r="D63">
-        <v>423</v>
+        <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F63" t="s">
         <v>11</v>
       </c>
       <c r="G63" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C64" t="s">
         <v>9</v>
       </c>
       <c r="D64">
-        <v>454</v>
+        <v>68</v>
       </c>
       <c r="E64" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F64" t="s">
         <v>11</v>
       </c>
       <c r="G64" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C65" t="s">
         <v>9</v>
       </c>
       <c r="D65">
-        <v>459</v>
+        <v>69</v>
       </c>
       <c r="E65" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="F65" t="s">
         <v>11</v>
       </c>
       <c r="G65" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C66" t="s">
         <v>9</v>
       </c>
       <c r="D66">
-        <v>465</v>
+        <v>70</v>
       </c>
       <c r="E66" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="F66" t="s">
         <v>11</v>
       </c>
       <c r="G66" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C67" t="s">
         <v>9</v>
       </c>
       <c r="D67">
-        <v>465</v>
+        <v>71</v>
       </c>
       <c r="E67" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="F67" t="s">
         <v>11</v>
       </c>
       <c r="G67" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C68" t="s">
         <v>9</v>
       </c>
       <c r="D68">
-        <v>474</v>
+        <v>332</v>
       </c>
       <c r="E68" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="F68" t="s">
         <v>11</v>
       </c>
       <c r="G68" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B69" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C69" t="s">
         <v>9</v>
       </c>
       <c r="D69">
-        <v>476</v>
+        <v>332</v>
       </c>
       <c r="E69" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="F69" t="s">
         <v>11</v>
       </c>
       <c r="G69" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C70" t="s">
         <v>9</v>
       </c>
       <c r="D70">
-        <v>477</v>
+        <v>332</v>
       </c>
       <c r="E70" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="F70" t="s">
         <v>11</v>
       </c>
       <c r="G70" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C71" t="s">
         <v>9</v>
       </c>
       <c r="D71">
-        <v>478</v>
+        <v>340</v>
       </c>
       <c r="E71" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="F71" t="s">
         <v>11</v>
       </c>
       <c r="G71" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C72" t="s">
         <v>9</v>
       </c>
       <c r="D72">
-        <v>479</v>
+        <v>433</v>
       </c>
       <c r="E72" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F72" t="s">
         <v>11</v>
       </c>
       <c r="G72" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B73" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C73" t="s">
         <v>9</v>
       </c>
       <c r="D73">
-        <v>480</v>
+        <v>433</v>
       </c>
       <c r="E73" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="F73" t="s">
         <v>11</v>
       </c>
       <c r="G73" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
@@ -2462,551 +2439,551 @@
         <v>7</v>
       </c>
       <c r="B74" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C74" t="s">
         <v>9</v>
       </c>
       <c r="D74">
-        <v>597</v>
+        <v>501</v>
       </c>
       <c r="E74" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="F74" t="s">
         <v>11</v>
       </c>
       <c r="G74" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C75" t="s">
         <v>9</v>
       </c>
       <c r="D75">
-        <v>654</v>
+        <v>501</v>
       </c>
       <c r="E75" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="F75" t="s">
         <v>11</v>
       </c>
       <c r="G75" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B76" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C76" t="s">
         <v>9</v>
       </c>
       <c r="D76">
-        <v>655</v>
+        <v>128</v>
       </c>
       <c r="E76" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F76" t="s">
         <v>11</v>
       </c>
       <c r="G76" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C77" t="s">
         <v>9</v>
       </c>
       <c r="D77">
-        <v>656</v>
+        <v>161</v>
       </c>
       <c r="E77" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="F77" t="s">
         <v>11</v>
       </c>
       <c r="G77" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B78" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C78" t="s">
         <v>9</v>
       </c>
       <c r="D78">
-        <v>665</v>
+        <v>169</v>
       </c>
       <c r="E78" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="F78" t="s">
         <v>11</v>
       </c>
       <c r="G78" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B79" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C79" t="s">
         <v>9</v>
       </c>
       <c r="D79">
-        <v>666</v>
+        <v>312</v>
       </c>
       <c r="E79" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="F79" t="s">
         <v>11</v>
       </c>
       <c r="G79" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C80" t="s">
         <v>9</v>
       </c>
       <c r="D80">
-        <v>667</v>
+        <v>312</v>
       </c>
       <c r="E80" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="F80" t="s">
         <v>11</v>
       </c>
       <c r="G80" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C81" t="s">
         <v>9</v>
       </c>
       <c r="D81">
-        <v>668</v>
+        <v>447</v>
       </c>
       <c r="E81" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="F81" t="s">
         <v>11</v>
       </c>
       <c r="G81" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C82" t="s">
         <v>9</v>
       </c>
       <c r="D82">
-        <v>669</v>
+        <v>481</v>
       </c>
       <c r="E82" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="F82" t="s">
         <v>11</v>
       </c>
       <c r="G82" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C83" t="s">
         <v>9</v>
       </c>
       <c r="D83">
-        <v>700</v>
+        <v>491</v>
       </c>
       <c r="E83" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="F83" t="s">
         <v>11</v>
       </c>
       <c r="G83" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="C84" t="s">
         <v>9</v>
       </c>
       <c r="D84">
-        <v>701</v>
+        <v>133</v>
       </c>
       <c r="E84" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F84" t="s">
         <v>11</v>
       </c>
       <c r="G84" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B85" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="C85" t="s">
         <v>9</v>
       </c>
       <c r="D85">
-        <v>706</v>
+        <v>160</v>
       </c>
       <c r="E85" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="F85" t="s">
         <v>11</v>
       </c>
       <c r="G85" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="C86" t="s">
         <v>9</v>
       </c>
       <c r="D86">
-        <v>744</v>
+        <v>170</v>
       </c>
       <c r="E86" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="F86" t="s">
         <v>11</v>
       </c>
       <c r="G86" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B87" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="C87" t="s">
         <v>9</v>
       </c>
       <c r="D87">
-        <v>755</v>
+        <v>136</v>
       </c>
       <c r="E87" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F87" t="s">
         <v>11</v>
       </c>
       <c r="G87" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="C88" t="s">
         <v>9</v>
       </c>
       <c r="D88">
-        <v>817</v>
+        <v>137</v>
       </c>
       <c r="E88" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F88" t="s">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="C89" t="s">
         <v>9</v>
       </c>
       <c r="D89">
-        <v>819</v>
+        <v>46</v>
       </c>
       <c r="E89" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="F89" t="s">
         <v>11</v>
       </c>
       <c r="G89" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B90" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="C90" t="s">
         <v>9</v>
       </c>
       <c r="D90">
-        <v>834</v>
+        <v>253</v>
       </c>
       <c r="E90" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F90" t="s">
         <v>11</v>
       </c>
       <c r="G90" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="C91" t="s">
         <v>9</v>
       </c>
       <c r="D91">
-        <v>847</v>
+        <v>177</v>
       </c>
       <c r="E91" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F91" t="s">
         <v>11</v>
       </c>
       <c r="G91" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B92" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="C92" t="s">
         <v>9</v>
       </c>
       <c r="D92">
-        <v>900</v>
+        <v>45</v>
       </c>
       <c r="E92" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="F92" t="s">
         <v>11</v>
       </c>
       <c r="G92" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B93" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="C93" t="s">
         <v>9</v>
       </c>
       <c r="D93">
-        <v>901</v>
+        <v>225</v>
       </c>
       <c r="E93" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="F93" t="s">
         <v>11</v>
       </c>
       <c r="G93" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B94" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="C94" t="s">
         <v>9</v>
       </c>
       <c r="D94">
-        <v>902</v>
+        <v>225</v>
       </c>
       <c r="E94" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F94" t="s">
         <v>11</v>
       </c>
       <c r="G94" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="C95" t="s">
         <v>9</v>
       </c>
       <c r="D95">
-        <v>903</v>
+        <v>167</v>
       </c>
       <c r="E95" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F95" t="s">
         <v>11</v>
       </c>
       <c r="G95" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="C96" t="s">
         <v>9</v>
       </c>
       <c r="D96">
-        <v>904</v>
+        <v>191</v>
       </c>
       <c r="E96" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="F96" t="s">
         <v>11</v>
       </c>
       <c r="G96" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="C97" t="s">
         <v>9</v>
       </c>
       <c r="D97">
-        <v>926</v>
+        <v>166</v>
       </c>
       <c r="E97" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F97" t="s">
         <v>11</v>
       </c>
       <c r="G97" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
@@ -3014,1423 +2991,214 @@
         <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="C98" t="s">
         <v>9</v>
       </c>
       <c r="D98">
-        <v>40</v>
+        <v>187</v>
       </c>
       <c r="E98" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="F98" t="s">
         <v>11</v>
       </c>
       <c r="G98" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>7</v>
-      </c>
-      <c r="B99" t="s">
-        <v>78</v>
-      </c>
-      <c r="C99" t="s">
-        <v>9</v>
-      </c>
-      <c r="D99">
-        <v>46</v>
-      </c>
-      <c r="E99" t="s">
-        <v>32</v>
-      </c>
-      <c r="F99" t="s">
-        <v>11</v>
-      </c>
-      <c r="G99" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>44</v>
-      </c>
-      <c r="B100" t="s">
-        <v>78</v>
-      </c>
-      <c r="C100" t="s">
-        <v>9</v>
-      </c>
-      <c r="D100">
-        <v>181</v>
-      </c>
-      <c r="E100" t="s">
-        <v>79</v>
-      </c>
-      <c r="F100" t="s">
-        <v>11</v>
-      </c>
-      <c r="G100" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>44</v>
-      </c>
-      <c r="B101" t="s">
-        <v>78</v>
-      </c>
-      <c r="C101" t="s">
-        <v>9</v>
-      </c>
-      <c r="D101">
-        <v>200</v>
-      </c>
-      <c r="E101" t="s">
-        <v>48</v>
-      </c>
-      <c r="F101" t="s">
-        <v>11</v>
-      </c>
-      <c r="G101" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>44</v>
-      </c>
-      <c r="B102" t="s">
-        <v>80</v>
-      </c>
-      <c r="C102" t="s">
-        <v>9</v>
-      </c>
-      <c r="D102">
-        <v>74</v>
-      </c>
-      <c r="E102" t="s">
-        <v>81</v>
-      </c>
-      <c r="F102" t="s">
-        <v>11</v>
-      </c>
-      <c r="G102" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>7</v>
-      </c>
-      <c r="B103" t="s">
-        <v>80</v>
-      </c>
-      <c r="C103" t="s">
-        <v>9</v>
-      </c>
-      <c r="D103">
-        <v>86</v>
-      </c>
-      <c r="E103" t="s">
-        <v>71</v>
-      </c>
-      <c r="F103" t="s">
-        <v>11</v>
-      </c>
-      <c r="G103" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>44</v>
-      </c>
-      <c r="B104" t="s">
-        <v>80</v>
-      </c>
-      <c r="C104" t="s">
-        <v>9</v>
-      </c>
-      <c r="D104">
-        <v>92</v>
-      </c>
-      <c r="E104" t="s">
-        <v>82</v>
-      </c>
-      <c r="F104" t="s">
-        <v>11</v>
-      </c>
-      <c r="G104" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>44</v>
-      </c>
-      <c r="B105" t="s">
-        <v>80</v>
-      </c>
-      <c r="C105" t="s">
-        <v>9</v>
-      </c>
-      <c r="D105">
-        <v>93</v>
-      </c>
-      <c r="E105" t="s">
-        <v>84</v>
-      </c>
-      <c r="F105" t="s">
-        <v>11</v>
-      </c>
-      <c r="G105" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>22</v>
-      </c>
-      <c r="B106" t="s">
-        <v>80</v>
-      </c>
-      <c r="C106" t="s">
-        <v>9</v>
-      </c>
-      <c r="D106">
-        <v>401</v>
-      </c>
-      <c r="E106" t="s">
-        <v>24</v>
-      </c>
-      <c r="F106" t="s">
-        <v>11</v>
-      </c>
-      <c r="G106" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>7</v>
-      </c>
-      <c r="B107" t="s">
-        <v>80</v>
-      </c>
-      <c r="C107" t="s">
-        <v>9</v>
-      </c>
-      <c r="D107">
-        <v>440</v>
-      </c>
-      <c r="E107" t="s">
-        <v>71</v>
-      </c>
-      <c r="F107" t="s">
-        <v>11</v>
-      </c>
-      <c r="G107" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>7</v>
-      </c>
-      <c r="B108" t="s">
-        <v>80</v>
-      </c>
-      <c r="C108" t="s">
-        <v>9</v>
-      </c>
-      <c r="D108">
-        <v>503</v>
-      </c>
-      <c r="E108" t="s">
-        <v>85</v>
-      </c>
-      <c r="F108" t="s">
-        <v>11</v>
-      </c>
-      <c r="G108" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>7</v>
-      </c>
-      <c r="B109" t="s">
-        <v>80</v>
-      </c>
-      <c r="C109" t="s">
-        <v>9</v>
-      </c>
-      <c r="D109">
-        <v>575</v>
-      </c>
-      <c r="E109" t="s">
-        <v>71</v>
-      </c>
-      <c r="F109" t="s">
-        <v>11</v>
-      </c>
-      <c r="G109" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>7</v>
-      </c>
-      <c r="B110" t="s">
-        <v>86</v>
-      </c>
-      <c r="C110" t="s">
-        <v>9</v>
-      </c>
-      <c r="D110">
-        <v>66</v>
-      </c>
-      <c r="E110" t="s">
-        <v>32</v>
-      </c>
-      <c r="F110" t="s">
-        <v>11</v>
-      </c>
-      <c r="G110" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>7</v>
-      </c>
-      <c r="B111" t="s">
-        <v>86</v>
-      </c>
-      <c r="C111" t="s">
-        <v>9</v>
-      </c>
-      <c r="D111">
-        <v>67</v>
-      </c>
-      <c r="E111" t="s">
-        <v>32</v>
-      </c>
-      <c r="F111" t="s">
-        <v>11</v>
-      </c>
-      <c r="G111" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>7</v>
-      </c>
-      <c r="B112" t="s">
-        <v>86</v>
-      </c>
-      <c r="C112" t="s">
-        <v>9</v>
-      </c>
-      <c r="D112">
-        <v>68</v>
-      </c>
-      <c r="E112" t="s">
-        <v>32</v>
-      </c>
-      <c r="F112" t="s">
-        <v>11</v>
-      </c>
-      <c r="G112" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>7</v>
-      </c>
-      <c r="B113" t="s">
-        <v>86</v>
-      </c>
-      <c r="C113" t="s">
-        <v>9</v>
-      </c>
-      <c r="D113">
         <v>69</v>
-      </c>
-      <c r="E113" t="s">
-        <v>32</v>
-      </c>
-      <c r="F113" t="s">
-        <v>11</v>
-      </c>
-      <c r="G113" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
-        <v>7</v>
-      </c>
-      <c r="B114" t="s">
-        <v>86</v>
-      </c>
-      <c r="C114" t="s">
-        <v>9</v>
-      </c>
-      <c r="D114">
-        <v>70</v>
-      </c>
-      <c r="E114" t="s">
-        <v>32</v>
-      </c>
-      <c r="F114" t="s">
-        <v>11</v>
-      </c>
-      <c r="G114" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>7</v>
-      </c>
-      <c r="B115" t="s">
-        <v>86</v>
-      </c>
-      <c r="C115" t="s">
-        <v>9</v>
-      </c>
-      <c r="D115">
-        <v>71</v>
-      </c>
-      <c r="E115" t="s">
-        <v>32</v>
-      </c>
-      <c r="F115" t="s">
-        <v>11</v>
-      </c>
-      <c r="G115" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>7</v>
-      </c>
-      <c r="B116" t="s">
-        <v>86</v>
-      </c>
-      <c r="C116" t="s">
-        <v>9</v>
-      </c>
-      <c r="D116">
-        <v>332</v>
-      </c>
-      <c r="E116" t="s">
-        <v>32</v>
-      </c>
-      <c r="F116" t="s">
-        <v>11</v>
-      </c>
-      <c r="G116" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
-        <v>44</v>
-      </c>
-      <c r="B117" t="s">
-        <v>86</v>
-      </c>
-      <c r="C117" t="s">
-        <v>9</v>
-      </c>
-      <c r="D117">
-        <v>332</v>
-      </c>
-      <c r="E117" t="s">
-        <v>87</v>
-      </c>
-      <c r="F117" t="s">
-        <v>11</v>
-      </c>
-      <c r="G117" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>44</v>
-      </c>
-      <c r="B118" t="s">
-        <v>86</v>
-      </c>
-      <c r="C118" t="s">
-        <v>9</v>
-      </c>
-      <c r="D118">
-        <v>332</v>
-      </c>
-      <c r="E118" t="s">
-        <v>88</v>
-      </c>
-      <c r="F118" t="s">
-        <v>11</v>
-      </c>
-      <c r="G118" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
-        <v>44</v>
-      </c>
-      <c r="B119" t="s">
-        <v>86</v>
-      </c>
-      <c r="C119" t="s">
-        <v>9</v>
-      </c>
-      <c r="D119">
-        <v>340</v>
-      </c>
-      <c r="E119" t="s">
-        <v>89</v>
-      </c>
-      <c r="F119" t="s">
-        <v>11</v>
-      </c>
-      <c r="G119" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>7</v>
-      </c>
-      <c r="B120" t="s">
-        <v>86</v>
-      </c>
-      <c r="C120" t="s">
-        <v>9</v>
-      </c>
-      <c r="D120">
-        <v>433</v>
-      </c>
-      <c r="E120" t="s">
-        <v>32</v>
-      </c>
-      <c r="F120" t="s">
-        <v>11</v>
-      </c>
-      <c r="G120" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>44</v>
-      </c>
-      <c r="B121" t="s">
-        <v>86</v>
-      </c>
-      <c r="C121" t="s">
-        <v>9</v>
-      </c>
-      <c r="D121">
-        <v>433</v>
-      </c>
-      <c r="E121" t="s">
-        <v>87</v>
-      </c>
-      <c r="F121" t="s">
-        <v>11</v>
-      </c>
-      <c r="G121" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>7</v>
-      </c>
-      <c r="B122" t="s">
-        <v>86</v>
-      </c>
-      <c r="C122" t="s">
-        <v>9</v>
-      </c>
-      <c r="D122">
-        <v>501</v>
-      </c>
-      <c r="E122" t="s">
-        <v>32</v>
-      </c>
-      <c r="F122" t="s">
-        <v>11</v>
-      </c>
-      <c r="G122" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
-        <v>44</v>
-      </c>
-      <c r="B123" t="s">
-        <v>86</v>
-      </c>
-      <c r="C123" t="s">
-        <v>9</v>
-      </c>
-      <c r="D123">
-        <v>501</v>
-      </c>
-      <c r="E123" t="s">
-        <v>87</v>
-      </c>
-      <c r="F123" t="s">
-        <v>11</v>
-      </c>
-      <c r="G123" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>7</v>
-      </c>
-      <c r="B124" t="s">
-        <v>86</v>
-      </c>
-      <c r="C124" t="s">
-        <v>9</v>
-      </c>
-      <c r="D124">
-        <v>552</v>
-      </c>
-      <c r="E124" t="s">
-        <v>90</v>
-      </c>
-      <c r="F124" t="s">
-        <v>40</v>
-      </c>
-      <c r="G124" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>22</v>
-      </c>
-      <c r="B125" t="s">
-        <v>91</v>
-      </c>
-      <c r="C125" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" t="s">
-        <v>29</v>
-      </c>
-      <c r="F125" t="s">
-        <v>11</v>
-      </c>
-      <c r="G125" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
-        <v>7</v>
-      </c>
-      <c r="B126" t="s">
-        <v>91</v>
-      </c>
-      <c r="C126" t="s">
-        <v>9</v>
-      </c>
-      <c r="D126">
-        <v>128</v>
-      </c>
-      <c r="E126" t="s">
-        <v>71</v>
-      </c>
-      <c r="F126" t="s">
-        <v>11</v>
-      </c>
-      <c r="G126" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>44</v>
-      </c>
-      <c r="B127" t="s">
-        <v>91</v>
-      </c>
-      <c r="C127" t="s">
-        <v>9</v>
-      </c>
-      <c r="D127">
-        <v>161</v>
-      </c>
-      <c r="E127" t="s">
-        <v>57</v>
-      </c>
-      <c r="F127" t="s">
-        <v>11</v>
-      </c>
-      <c r="G127" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
-        <v>7</v>
-      </c>
-      <c r="B128" t="s">
-        <v>91</v>
-      </c>
-      <c r="C128" t="s">
-        <v>9</v>
-      </c>
-      <c r="D128">
-        <v>169</v>
-      </c>
-      <c r="E128" t="s">
-        <v>92</v>
-      </c>
-      <c r="F128" t="s">
-        <v>11</v>
-      </c>
-      <c r="G128" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>44</v>
-      </c>
-      <c r="B129" t="s">
-        <v>91</v>
-      </c>
-      <c r="C129" t="s">
-        <v>9</v>
-      </c>
-      <c r="D129">
-        <v>312</v>
-      </c>
-      <c r="E129" t="s">
-        <v>93</v>
-      </c>
-      <c r="F129" t="s">
-        <v>11</v>
-      </c>
-      <c r="G129" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>7</v>
-      </c>
-      <c r="B130" t="s">
-        <v>91</v>
-      </c>
-      <c r="C130" t="s">
-        <v>9</v>
-      </c>
-      <c r="D130">
-        <v>312</v>
-      </c>
-      <c r="E130" t="s">
-        <v>95</v>
-      </c>
-      <c r="F130" t="s">
-        <v>11</v>
-      </c>
-      <c r="G130" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>44</v>
-      </c>
-      <c r="B131" t="s">
-        <v>91</v>
-      </c>
-      <c r="C131" t="s">
-        <v>9</v>
-      </c>
-      <c r="D131">
-        <v>447</v>
-      </c>
-      <c r="E131" t="s">
-        <v>96</v>
-      </c>
-      <c r="F131" t="s">
-        <v>11</v>
-      </c>
-      <c r="G131" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>7</v>
-      </c>
-      <c r="B132" t="s">
-        <v>91</v>
-      </c>
-      <c r="C132" t="s">
-        <v>9</v>
-      </c>
-      <c r="D132">
-        <v>481</v>
-      </c>
-      <c r="E132" t="s">
-        <v>92</v>
-      </c>
-      <c r="F132" t="s">
-        <v>11</v>
-      </c>
-      <c r="G132" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>44</v>
-      </c>
-      <c r="B133" t="s">
-        <v>91</v>
-      </c>
-      <c r="C133" t="s">
-        <v>9</v>
-      </c>
-      <c r="D133">
-        <v>491</v>
-      </c>
-      <c r="E133" t="s">
-        <v>98</v>
-      </c>
-      <c r="F133" t="s">
-        <v>11</v>
-      </c>
-      <c r="G133" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>7</v>
-      </c>
-      <c r="B134" t="s">
-        <v>99</v>
-      </c>
-      <c r="C134" t="s">
-        <v>9</v>
-      </c>
-      <c r="D134">
-        <v>133</v>
-      </c>
-      <c r="E134" t="s">
-        <v>71</v>
-      </c>
-      <c r="F134" t="s">
-        <v>11</v>
-      </c>
-      <c r="G134" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>44</v>
-      </c>
-      <c r="B135" t="s">
-        <v>99</v>
-      </c>
-      <c r="C135" t="s">
-        <v>9</v>
-      </c>
-      <c r="D135">
-        <v>160</v>
-      </c>
-      <c r="E135" t="s">
-        <v>93</v>
-      </c>
-      <c r="F135" t="s">
-        <v>11</v>
-      </c>
-      <c r="G135" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>7</v>
-      </c>
-      <c r="B136" t="s">
-        <v>99</v>
-      </c>
-      <c r="C136" t="s">
-        <v>9</v>
-      </c>
-      <c r="D136">
-        <v>170</v>
-      </c>
-      <c r="E136" t="s">
-        <v>92</v>
-      </c>
-      <c r="F136" t="s">
-        <v>11</v>
-      </c>
-      <c r="G136" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>22</v>
-      </c>
-      <c r="B137" t="s">
-        <v>99</v>
-      </c>
-      <c r="C137" t="s">
-        <v>9</v>
-      </c>
-      <c r="D137">
-        <v>227</v>
-      </c>
-      <c r="E137" t="s">
-        <v>24</v>
-      </c>
-      <c r="F137" t="s">
-        <v>11</v>
-      </c>
-      <c r="G137" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>22</v>
-      </c>
-      <c r="B138" t="s">
-        <v>99</v>
-      </c>
-      <c r="C138" t="s">
-        <v>9</v>
-      </c>
-      <c r="D138">
-        <v>228</v>
-      </c>
-      <c r="E138" t="s">
-        <v>24</v>
-      </c>
-      <c r="F138" t="s">
-        <v>11</v>
-      </c>
-      <c r="G138" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>7</v>
-      </c>
-      <c r="B139" t="s">
-        <v>100</v>
-      </c>
-      <c r="C139" t="s">
-        <v>9</v>
-      </c>
-      <c r="D139">
-        <v>136</v>
-      </c>
-      <c r="E139" t="s">
-        <v>71</v>
-      </c>
-      <c r="F139" t="s">
-        <v>11</v>
-      </c>
-      <c r="G139" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>44</v>
-      </c>
-      <c r="B140" t="s">
-        <v>100</v>
-      </c>
-      <c r="C140" t="s">
-        <v>9</v>
-      </c>
-      <c r="D140">
-        <v>137</v>
-      </c>
-      <c r="E140" t="s">
-        <v>48</v>
-      </c>
-      <c r="F140" t="s">
-        <v>11</v>
-      </c>
-      <c r="G140" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>44</v>
-      </c>
-      <c r="B141" t="s">
-        <v>101</v>
-      </c>
-      <c r="C141" t="s">
-        <v>9</v>
-      </c>
-      <c r="D141">
-        <v>46</v>
-      </c>
-      <c r="E141" t="s">
-        <v>79</v>
-      </c>
-      <c r="F141" t="s">
-        <v>11</v>
-      </c>
-      <c r="G141" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>7</v>
-      </c>
-      <c r="B142" t="s">
-        <v>101</v>
-      </c>
-      <c r="C142" t="s">
-        <v>9</v>
-      </c>
-      <c r="D142">
-        <v>253</v>
-      </c>
-      <c r="E142" t="s">
-        <v>85</v>
-      </c>
-      <c r="F142" t="s">
-        <v>11</v>
-      </c>
-      <c r="G142" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>7</v>
-      </c>
-      <c r="B143" t="s">
-        <v>102</v>
-      </c>
-      <c r="C143" t="s">
-        <v>9</v>
-      </c>
-      <c r="D143">
-        <v>177</v>
-      </c>
-      <c r="E143" t="s">
-        <v>85</v>
-      </c>
-      <c r="F143" t="s">
-        <v>11</v>
-      </c>
-      <c r="G143" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>44</v>
-      </c>
-      <c r="B144" t="s">
-        <v>103</v>
-      </c>
-      <c r="C144" t="s">
-        <v>9</v>
-      </c>
-      <c r="D144">
-        <v>45</v>
-      </c>
-      <c r="E144" t="s">
-        <v>104</v>
-      </c>
-      <c r="F144" t="s">
-        <v>11</v>
-      </c>
-      <c r="G144" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>44</v>
-      </c>
-      <c r="B145" t="s">
-        <v>103</v>
-      </c>
-      <c r="C145" t="s">
-        <v>9</v>
-      </c>
-      <c r="D145">
-        <v>225</v>
-      </c>
-      <c r="E145" t="s">
-        <v>106</v>
-      </c>
-      <c r="F145" t="s">
-        <v>11</v>
-      </c>
-      <c r="G145" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>7</v>
-      </c>
-      <c r="B146" t="s">
-        <v>103</v>
-      </c>
-      <c r="C146" t="s">
-        <v>9</v>
-      </c>
-      <c r="D146">
-        <v>225</v>
-      </c>
-      <c r="E146" t="s">
-        <v>71</v>
-      </c>
-      <c r="F146" t="s">
-        <v>11</v>
-      </c>
-      <c r="G146" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>7</v>
-      </c>
-      <c r="B147" t="s">
-        <v>108</v>
-      </c>
-      <c r="C147" t="s">
-        <v>9</v>
-      </c>
-      <c r="D147">
-        <v>167</v>
-      </c>
-      <c r="E147" t="s">
-        <v>71</v>
-      </c>
-      <c r="F147" t="s">
-        <v>11</v>
-      </c>
-      <c r="G147" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>7</v>
-      </c>
-      <c r="B148" t="s">
-        <v>109</v>
-      </c>
-      <c r="C148" t="s">
-        <v>9</v>
-      </c>
-      <c r="D148">
-        <v>191</v>
-      </c>
-      <c r="E148" t="s">
-        <v>85</v>
-      </c>
-      <c r="F148" t="s">
-        <v>11</v>
-      </c>
-      <c r="G148" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>7</v>
-      </c>
-      <c r="B149" t="s">
-        <v>110</v>
-      </c>
-      <c r="C149" t="s">
-        <v>9</v>
-      </c>
-      <c r="D149">
-        <v>166</v>
-      </c>
-      <c r="E149" t="s">
-        <v>85</v>
-      </c>
-      <c r="F149" t="s">
-        <v>11</v>
-      </c>
-      <c r="G149" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>7</v>
-      </c>
-      <c r="B150" t="s">
-        <v>111</v>
-      </c>
-      <c r="C150" t="s">
-        <v>9</v>
-      </c>
-      <c r="D150">
-        <v>187</v>
-      </c>
-      <c r="E150" t="s">
-        <v>71</v>
-      </c>
-      <c r="F150" t="s">
-        <v>11</v>
-      </c>
-      <c r="G150" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="93.7265625" customWidth="1"/>
-    <col min="2" max="2" width="10.1796875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="106.36328125" customWidth="1"/>
+    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>113</v>
+      <c r="A1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="4">
-        <v>49</v>
+        <v>110</v>
+      </c>
+      <c r="B2">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" s="4">
-        <v>16</v>
+        <v>111</v>
+      </c>
+      <c r="B3">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="4">
-        <v>14</v>
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="4">
-        <v>12</v>
+        <v>112</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B6" s="4">
-        <v>10</v>
+        <v>113</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" s="4">
+        <v>114</v>
+      </c>
+      <c r="B7">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8" s="4">
-        <v>8</v>
+        <v>115</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B9" s="4">
-        <v>4</v>
+        <v>84</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="4">
+        <v>36</v>
+      </c>
+      <c r="B10">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="4">
+        <v>35</v>
+      </c>
+      <c r="B11">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="4">
+        <v>88</v>
+      </c>
+      <c r="B12">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>92</v>
-      </c>
-      <c r="B13" s="4">
+        <v>45</v>
+      </c>
+      <c r="B13">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="4">
-        <v>3</v>
+        <v>116</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B15" s="4">
+        <v>117</v>
+      </c>
+      <c r="B15">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="4">
-        <v>2</v>
+        <v>118</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>122</v>
-      </c>
-      <c r="B17" s="4">
-        <v>2</v>
+        <v>119</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>119</v>
-      </c>
-      <c r="B18" s="4">
+        <v>23</v>
+      </c>
+      <c r="B18">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>120</v>
-      </c>
-      <c r="B19" s="4">
+        <v>44</v>
+      </c>
+      <c r="B19">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="4">
+        <v>120</v>
+      </c>
+      <c r="B20">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="4">
+        <v>94</v>
+      </c>
+      <c r="B21">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B24" s="4">
-        <f>SUM(B2:B23)</f>
-        <v>148</v>
+      <c r="B22">
+        <f>SUM(B2:B21)</f>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>